--- a/data/trans_bre/P6903-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P6903-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 29,01</t>
+          <t>-10,02; 29,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 33,07</t>
+          <t>-5,81; 31,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,5; 23,39</t>
+          <t>-19,39; 24,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 26,47</t>
+          <t>-7,98; 25,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,47; 144,75</t>
+          <t>-30,8; 150,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,69; 181,22</t>
+          <t>-23,15; 170,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-48,22; 95,12</t>
+          <t>-45,57; 100,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 138,43</t>
+          <t>-21,11; 125,32</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,35; 4,21</t>
+          <t>-23,62; 4,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 28,73</t>
+          <t>-3,3; 27,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 29,06</t>
+          <t>-6,21; 26,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 15,27</t>
+          <t>-10,91; 16,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,73; 20,16</t>
+          <t>-63,81; 16,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 175,2</t>
+          <t>-12,04; 170,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 109,5</t>
+          <t>-17,41; 97,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-24,49; 54,56</t>
+          <t>-22,68; 55,3</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 25,68</t>
+          <t>-7,78; 24,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 17,73</t>
+          <t>-15,52; 17,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 20,0</t>
+          <t>-11,85; 21,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-37,42; 11,84</t>
+          <t>-40,63; 9,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,79; 136,08</t>
+          <t>-27,98; 124,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-44,54; 81,77</t>
+          <t>-46,16; 84,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-24,43; 56,3</t>
+          <t>-24,23; 59,81</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-75,12; 33,03</t>
+          <t>-71,69; 26,47</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 7,39</t>
+          <t>-17,71; 8,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,14; 34,4</t>
+          <t>2,6; 33,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,61; 9,27</t>
+          <t>-22,92; 9,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,94; 30,3</t>
+          <t>3,69; 29,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,03; 23,59</t>
+          <t>-41,59; 25,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 267,73</t>
+          <t>5,07; 247,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,29; 26,19</t>
+          <t>-46,08; 24,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,53; 137,31</t>
+          <t>8,33; 124,06</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 8,23</t>
+          <t>-8,31; 6,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,61; 18,66</t>
+          <t>2,58; 18,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 12,36</t>
+          <t>-6,82; 10,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 12,81</t>
+          <t>-7,46; 13,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 30,33</t>
+          <t>-24,54; 22,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,93; 90,77</t>
+          <t>9,93; 90,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,05; 35,28</t>
+          <t>-16,05; 30,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 41,7</t>
+          <t>-19,01; 43,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6903-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P6903-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,2</t>
+          <t>8,71</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 29,88</t>
+          <t>-10,62; 30,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 31,51</t>
+          <t>-8,1; 31,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,39; 24,51</t>
+          <t>-18,33; 24,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 25,58</t>
+          <t>-7,48; 25,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 150,87</t>
+          <t>-33,6; 156,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 170,34</t>
+          <t>-29,38; 163,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-45,57; 100,22</t>
+          <t>-43,35; 100,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,11; 125,32</t>
+          <t>-19,56; 124,4</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,91</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 4,22</t>
+          <t>-22,59; 5,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 27,55</t>
+          <t>-3,61; 28,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 26,4</t>
+          <t>-4,7; 28,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 16,3</t>
+          <t>-11,17; 13,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,81; 16,35</t>
+          <t>-62,61; 20,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 170,63</t>
+          <t>-16,01; 165,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,41; 97,44</t>
+          <t>-12,85; 105,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-22,68; 55,3</t>
+          <t>-24,36; 40,85</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-10,92</t>
+          <t>5,58</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-27,98%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 24,45</t>
+          <t>-8,68; 25,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 17,48</t>
+          <t>-15,28; 16,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,85; 21,07</t>
+          <t>-11,57; 19,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-40,63; 9,31</t>
+          <t>-12,28; 22,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,98; 124,05</t>
+          <t>-29,54; 125,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,16; 84,51</t>
+          <t>-46,14; 84,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-24,23; 59,81</t>
+          <t>-25,58; 54,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-71,69; 26,47</t>
+          <t>-25,0; 86,07</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,24</t>
+          <t>12,41</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>37,48%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 8,23</t>
+          <t>-18,6; 6,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 33,52</t>
+          <t>3,54; 31,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 9,04</t>
+          <t>-24,8; 8,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 29,73</t>
+          <t>-0,6; 23,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,59; 25,81</t>
+          <t>-42,63; 21,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 247,64</t>
+          <t>10,93; 255,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,08; 24,74</t>
+          <t>-47,56; 22,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,33; 124,06</t>
+          <t>-0,14; 91,41</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,9</t>
+          <t>6,63</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 6,57</t>
+          <t>-8,59; 6,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 18,79</t>
+          <t>2,07; 19,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 10,76</t>
+          <t>-6,24; 11,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 13,31</t>
+          <t>-1,68; 13,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,54; 22,58</t>
+          <t>-25,27; 23,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,93; 90,61</t>
+          <t>7,63; 94,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 30,3</t>
+          <t>-13,89; 33,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 43,48</t>
+          <t>-4,31; 42,85</t>
         </is>
       </c>
     </row>
